--- a/Output/arima_model_interruption2_weekly_output.xlsx
+++ b/Output/arima_model_interruption2_weekly_output.xlsx
@@ -1513,7 +1513,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Food Colour/Flavour and Baking Additivies</t>
+          <t>Food Colour/Flavour and Baking Additives</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Sweet Snacks/Baked Foods</t>
+          <t>Sweet Snacks/Sweet Baked Foods</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -4973,7 +4973,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Food Colour/Flavour and Baking Additivies</t>
+          <t>Food Colour/Flavour and Baking Additives</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -5252,7 +5252,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Sweet Snacks/Baked Foods</t>
+          <t>Sweet Snacks/Sweet Baked Foods</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -8752,7 +8752,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Food Colour/Flavour and Baking Additivies</t>
+          <t>Food Colour/Flavour and Baking Additives</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -8787,7 +8787,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Food Colour/Flavour and Baking Additivies</t>
+          <t>Food Colour/Flavour and Baking Additives</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -8822,7 +8822,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Food Colour/Flavour and Baking Additivies</t>
+          <t>Food Colour/Flavour and Baking Additives</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -8857,7 +8857,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Food Colour/Flavour and Baking Additivies</t>
+          <t>Food Colour/Flavour and Baking Additives</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -8892,7 +8892,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Food Colour/Flavour and Baking Additivies</t>
+          <t>Food Colour/Flavour and Baking Additives</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -8927,7 +8927,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Food Colour/Flavour and Baking Additivies</t>
+          <t>Food Colour/Flavour and Baking Additives</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -8962,7 +8962,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Food Colour/Flavour and Baking Additivies</t>
+          <t>Food Colour/Flavour and Baking Additives</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -8997,7 +8997,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Food Colour/Flavour and Baking Additivies</t>
+          <t>Food Colour/Flavour and Baking Additives</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -11132,7 +11132,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Sweet Snacks/Baked Foods</t>
+          <t>Sweet Snacks/Sweet Baked Foods</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -11167,7 +11167,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Sweet Snacks/Baked Foods</t>
+          <t>Sweet Snacks/Sweet Baked Foods</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -11202,7 +11202,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Sweet Snacks/Baked Foods</t>
+          <t>Sweet Snacks/Sweet Baked Foods</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -11237,7 +11237,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Sweet Snacks/Baked Foods</t>
+          <t>Sweet Snacks/Sweet Baked Foods</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -11272,7 +11272,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Sweet Snacks/Baked Foods</t>
+          <t>Sweet Snacks/Sweet Baked Foods</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -11307,7 +11307,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Sweet Snacks/Baked Foods</t>
+          <t>Sweet Snacks/Sweet Baked Foods</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -17366,7 +17366,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Food Colour/Flavour and Baking Additivies</t>
+          <t>Food Colour/Flavour and Baking Additives</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -17834,7 +17834,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Sweet Snacks/Baked Foods</t>
+          <t>Sweet Snacks/Sweet Baked Foods</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
